--- a/adopt_net0/database/templates/technology_data/Industrial/WasteCaL_data/wasteCaL_sheet.xlsx
+++ b/adopt_net0/database/templates/technology_data/Industrial/WasteCaL_data/wasteCaL_sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0954659\PycharmProjects\AdOpT-NET0_luca\adopt_net0\database\templates\technology_data\Industrial\WasteCaL_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{488FB849-ECF7-47ED-8C3D-65A7492CABAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE0923B7-CDDE-4392-BC55-4FA90E9AF4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F88CED2-51E2-4BD6-898E-4BEA1BA4A2AA}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8F88CED2-51E2-4BD6-898E-4BEA1BA4A2AA}"/>
   </bookViews>
   <sheets>
     <sheet name="capex_eur" sheetId="1" r:id="rId1"/>
@@ -616,13 +616,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB530849-3AC0-454A-9B3C-7EE06DFB619F}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1">
         <v>0.08</v>
       </c>
@@ -630,20 +630,18 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
-        <f>_xlfn.FORECAST.LINEAR(A2,B3:B4,A3:A4)</f>
-        <v>64309181.579637378</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <f>_xlfn.FORECAST.LINEAR(A2,C3:C4,A3:A4)</f>
-        <v>61895023.564156741</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>3347.0983994063113</v>
       </c>
@@ -655,7 +653,7 @@
       </c>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>8925.5957317501616</v>
       </c>
@@ -666,7 +664,7 @@
         <v>396717686.00048</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>16066.072317150292</v>
       </c>
@@ -677,7 +675,7 @@
         <v>586394103.56009102</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>34000</v>
       </c>
@@ -690,19 +688,19 @@
         <v>1062782915.2832865</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
     </row>
   </sheetData>
@@ -714,12 +712,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED8393E1-2116-44F4-BC6A-7CAB75645393}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B1">
         <v>0.08</v>
       </c>
@@ -727,7 +725,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -738,7 +736,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -760,13 +758,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{360CA07C-9042-4182-B481-990E6A122527}">
   <dimension ref="A2:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -777,7 +775,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -788,7 +786,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -799,7 +797,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -810,7 +808,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -829,17 +827,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3800F7-44EF-4E95-8339-2B9D4ABCCCA3}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.44140625" customWidth="1"/>
-    <col min="4" max="4" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
         <v>18</v>
       </c>
@@ -850,7 +848,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -870,7 +868,7 @@
         <v>0.1285572943289566</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -890,7 +888,7 @@
         <v>0.12513581457033682</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -910,7 +908,7 @@
         <v>0.13047121888388721</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -930,7 +928,7 @@
         <v>0.12480663803176834</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -950,7 +948,7 @@
         <v>0.12562956888190682</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>17</v>
       </c>
@@ -961,7 +959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -985,7 +983,7 @@
         <v>0.1285572943289566</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1009,7 +1007,7 @@
         <v>0.12513581457033682</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1033,7 +1031,7 @@
         <v>0.13047121888388721</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1057,7 +1055,7 @@
         <v>0.12480663803176834</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1081,7 +1079,7 @@
         <v>0.12562956888190682</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
         <v>17</v>
       </c>
@@ -1098,7 +1096,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -1120,7 +1118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1150,7 +1148,7 @@
         <v>-0.38825764055897322</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -1180,7 +1178,7 @@
         <v>-0.21718551162933217</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -1210,7 +1208,7 @@
         <v>2.917497849317642</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -1248,18 +1246,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{808567DB-59C1-42B3-8939-773BE0BF59FD}">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="71.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="71.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>21</v>
       </c>
@@ -1282,7 +1280,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1309,7 +1307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1343,7 +1341,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -1374,7 +1372,7 @@
         <v>-0.21718551162933217</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1405,7 +1403,7 @@
         <v>2.917497849317642</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
